--- a/sharing_consent_forms/033_donor_quote_publication_consent_form--sharing_consent_forms.xlsx
+++ b/sharing_consent_forms/033_donor_quote_publication_consent_form--sharing_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'i_grant_permission_for_jotform_to_share_and_publish_my_quote_in_any_form_or_medium.'}</t>
+          <t>i_grant_permission_for_jotform_to_share_and_publish_my_quote_in_any_form_or_medium.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'I grant permission for Jotform to share and publish my quote in any form or medium.'}</t>
+          <t>I grant permission for Jotform to share and publish my quote in any form or medium.</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'i_do_not_grant_permission_for_jotform_to_share_and_publish_my_quote_in_any_form_or_medium.'}</t>
+          <t>i_do_not_grant_permission_for_jotform_to_share_and_publish_my_quote_in_any_form_or_medium.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'I do not grant permission for Jotform to share and publish my quote in any form or medium.'}</t>
+          <t>I do not grant permission for Jotform to share and publish my quote in any form or medium.</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'website'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Website'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
